--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR - SKA LOGISTIK C.B. ANDÚJAR.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAISO INTERIOR - SKA LOGISTIK C.B. ANDÚJAR.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ GUZMÁN</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9215</v>
+        <v>5.306500000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9215</v>
+        <v>7.4336</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-2.1268</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9215</v>
+        <v>7.700500000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9081000000000001</v>
+        <v>16.8328</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0134</v>
+        <v>-9.132599999999998</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9215</v>
+        <v>42.1888</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9081000000000001</v>
+        <v>34.7237</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0134</v>
+        <v>7.4655</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-34.4885</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-17.8908</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>-16.5978</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-14.0739</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-59.8634</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>45.7896</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-5.258900000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-5.0396</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-0.2190000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>16.939</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>30.1478</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-13.2085</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>J. MARTÍNEZ GUZMÁN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>1.886700000000001</v>
+        <v>3.9215</v>
       </c>
       <c r="E4" t="n">
-        <v>16.4084</v>
+        <v>3.9215</v>
       </c>
       <c r="F4" t="n">
-        <v>-14.5218</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>-19.7762</v>
+        <v>3.9215</v>
       </c>
       <c r="H4" t="n">
-        <v>1.625</v>
+        <v>0.9081000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>-21.4008</v>
+        <v>3.0134</v>
       </c>
       <c r="J4" t="n">
-        <v>24.5237</v>
+        <v>3.9215</v>
       </c>
       <c r="K4" t="n">
-        <v>24.2178</v>
+        <v>0.9081000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3059000000000002</v>
+        <v>3.0134</v>
       </c>
       <c r="M4" t="n">
-        <v>-44.2998</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-22.5929</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-21.707</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-11.1002</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-63.2329</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>52.1325</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>27.6664</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>20.2981</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>7.368399999999999</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>5.097099999999999</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>34.8202</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-29.7231</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. VALENZUELA COCA</t>
+          <t>R. ALMAGRO LAZARO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0002</v>
+        <v>0.2135</v>
       </c>
       <c r="E5" t="n">
-        <v>0.244</v>
+        <v>0.6727</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2442</v>
+        <v>-0.4591000000000002</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6047</v>
+        <v>0.2537000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.218</v>
+        <v>-0.6837000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8227</v>
+        <v>0.9374</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3136</v>
+        <v>2.7648</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3499</v>
+        <v>1.3185</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0363</v>
+        <v>1.4465</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9184</v>
+        <v>-2.5111</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1319</v>
+        <v>-2.002</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7864</v>
+        <v>-0.5091000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5947</v>
+        <v>0.3964</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>-1.784</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3964</v>
+        <v>2.1804</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4658</v>
+        <v>-0.2405</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9215</v>
+        <v>-0.3082</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5443</v>
+        <v>0.06789999999999996</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2666</v>
+        <v>-0.1962</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2666</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. ALMAGRO LAZARO</t>
+          <t>T. VALENZUELA COCA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,70 +874,70 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.06719999999999959</v>
+        <v>-0.5271</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6726999999999999</v>
+        <v>-0.3672</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7399000000000002</v>
+        <v>-0.1599</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2537000000000001</v>
+        <v>-0.6047</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6837000000000001</v>
+        <v>0.218</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9374</v>
+        <v>-0.8227</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7648</v>
+        <v>0.3136</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3185</v>
+        <v>0.3499</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4465</v>
+        <v>-0.0363</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.5111</v>
+        <v>-0.9184</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.002</v>
+        <v>-0.1319</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5091000000000001</v>
+        <v>-0.7864</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.5947</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.9911</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.3964</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.784</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.1804</v>
-      </c>
       <c r="S6" t="n">
-        <v>-0.5212000000000001</v>
+        <v>0.9388</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3083</v>
+        <v>0.3103</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2131</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1962</v>
+        <v>-0.2666</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1962</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.45</v>
+        <v>-1.9511</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6049</v>
+        <v>-0.9936</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8451</v>
+        <v>-0.9574</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6026</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0366</v>
+        <v>-0.5378000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0498</v>
+        <v>-0.4385</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01300000000000001</v>
+        <v>-0.09929999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>A. GUTIERREZ MORENO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.821900000000001</v>
+        <v>-7.7923</v>
       </c>
       <c r="E8" t="n">
-        <v>4.742900000000001</v>
+        <v>-2.7932</v>
       </c>
       <c r="F8" t="n">
-        <v>-9.564399999999999</v>
+        <v>-4.999099999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>7.700500000000001</v>
+        <v>-5.3099</v>
       </c>
       <c r="H8" t="n">
-        <v>16.8328</v>
+        <v>-2.5626</v>
       </c>
       <c r="I8" t="n">
-        <v>-9.132599999999998</v>
+        <v>-2.7474</v>
       </c>
       <c r="J8" t="n">
-        <v>42.1888</v>
+        <v>-0.5706</v>
       </c>
       <c r="K8" t="n">
-        <v>34.7237</v>
+        <v>-0.6186</v>
       </c>
       <c r="L8" t="n">
-        <v>7.4655</v>
+        <v>0.048</v>
       </c>
       <c r="M8" t="n">
-        <v>-34.4885</v>
+        <v>-4.7394</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.8908</v>
+        <v>-1.9441</v>
       </c>
       <c r="O8" t="n">
-        <v>-16.5978</v>
+        <v>-2.7954</v>
       </c>
       <c r="P8" t="n">
-        <v>-14.0739</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q8" t="n">
-        <v>-59.8634</v>
+        <v>-1.9822</v>
       </c>
       <c r="R8" t="n">
-        <v>45.7896</v>
+        <v>1.3875</v>
       </c>
       <c r="S8" t="n">
-        <v>-15.387</v>
+        <v>-1.5005</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.7304</v>
+        <v>-0.2402</v>
       </c>
       <c r="U8" t="n">
-        <v>-7.6569</v>
+        <v>-1.26</v>
       </c>
       <c r="V8" t="n">
-        <v>16.939</v>
+        <v>-0.3873</v>
       </c>
       <c r="W8" t="n">
-        <v>30.1478</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-13.2085</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K. DOMINGOS</t>
+          <t>D. BUSTO VERANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.4623</v>
+        <v>-9.4785</v>
       </c>
       <c r="E9" t="n">
-        <v>3.655800000000002</v>
+        <v>-8.8422</v>
       </c>
       <c r="F9" t="n">
-        <v>-9.118</v>
+        <v>-0.6361999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>2.385800000000001</v>
+        <v>-8.8813</v>
       </c>
       <c r="H9" t="n">
-        <v>6.503399999999999</v>
+        <v>-4.8849</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.1171</v>
+        <v>-3.9966</v>
       </c>
       <c r="J9" t="n">
-        <v>15.689</v>
+        <v>-6.1241</v>
       </c>
       <c r="K9" t="n">
-        <v>13.6801</v>
+        <v>-4.3227</v>
       </c>
       <c r="L9" t="n">
-        <v>2.009</v>
+        <v>-1.8015</v>
       </c>
       <c r="M9" t="n">
-        <v>-13.3032</v>
+        <v>-2.7571</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.1768</v>
+        <v>-0.5622</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.1264</v>
+        <v>-2.195</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.0471</v>
+        <v>-0.3963999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-32.7067</v>
+        <v>-3.1716</v>
       </c>
       <c r="R9" t="n">
-        <v>15.6597</v>
+        <v>2.7751</v>
       </c>
       <c r="S9" t="n">
-        <v>13.3241</v>
+        <v>-0.4672</v>
       </c>
       <c r="T9" t="n">
-        <v>12.8021</v>
+        <v>-1.02</v>
       </c>
       <c r="U9" t="n">
-        <v>0.522</v>
+        <v>0.5529000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.1252</v>
+        <v>0.2665999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>7.8714</v>
+        <v>1.4737</v>
       </c>
       <c r="X9" t="n">
-        <v>-11.9966</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MORENO</t>
+          <t>A. TORIL RAYO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.606400000000001</v>
+        <v>-11.5385</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.4668</v>
+        <v>-6.9999</v>
       </c>
       <c r="F10" t="n">
-        <v>-5.1395</v>
+        <v>-4.5389</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.3099</v>
+        <v>-6.1878</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5626</v>
+        <v>-4.3125</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7474</v>
+        <v>-1.8755</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5706</v>
+        <v>5.7936</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6186</v>
+        <v>3.1832</v>
       </c>
       <c r="L10" t="n">
-        <v>0.048</v>
+        <v>2.6104</v>
       </c>
       <c r="M10" t="n">
-        <v>-4.7394</v>
+        <v>-11.9816</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.9441</v>
+        <v>-7.495799999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.7954</v>
+        <v>-4.4859</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>-12.6861</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3875</v>
+        <v>14.0736</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3144</v>
+        <v>-1.9621</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9139</v>
+        <v>-1.1735</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.4005</v>
+        <v>-0.7885000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3873</v>
+        <v>-4.7763</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0663</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3873</v>
+        <v>-5.842600000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. BUSTO VERANO</t>
+          <t>M. BAMADU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.352399999999999</v>
+        <v>-11.6424</v>
       </c>
       <c r="E11" t="n">
-        <v>-9.249700000000001</v>
+        <v>-6.2324</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1027999999999998</v>
+        <v>-5.41</v>
       </c>
       <c r="G11" t="n">
-        <v>-8.8813</v>
+        <v>-8.055099999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-4.8849</v>
+        <v>0.2692000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.9966</v>
+        <v>-8.324300000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.1241</v>
+        <v>-1.0777</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.3227</v>
+        <v>2.1936</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8015</v>
+        <v>-3.2712</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.7571</v>
+        <v>-6.9775</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5622</v>
+        <v>-1.9244</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.195</v>
+        <v>-5.0531</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3963999999999999</v>
+        <v>-1.3877</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.1716</v>
+        <v>-5.153700000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>2.7751</v>
+        <v>3.7662</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3412000000000001</v>
+        <v>-0.9222999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4276</v>
+        <v>-1.1376</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0863</v>
+        <v>0.2154</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2665999999999999</v>
+        <v>-1.2775</v>
       </c>
       <c r="W11" t="n">
-        <v>1.4737</v>
+        <v>1.1367</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2071</v>
+        <v>-2.4142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. TORIL RAYO</t>
+          <t>F. JIMENEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>-11.2171</v>
+        <v>-14.9083</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.2743</v>
+        <v>-13.3643</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.9426</v>
+        <v>-1.544</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.1878</v>
+        <v>-10.8337</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.3125</v>
+        <v>-4.3382</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8755</v>
+        <v>-6.4955</v>
       </c>
       <c r="J12" t="n">
-        <v>5.7936</v>
+        <v>-4.0913</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1832</v>
+        <v>0.09630000000000005</v>
       </c>
       <c r="L12" t="n">
-        <v>2.6104</v>
+        <v>-4.1875</v>
       </c>
       <c r="M12" t="n">
-        <v>-11.9816</v>
+        <v>-6.7424</v>
       </c>
       <c r="N12" t="n">
-        <v>-7.495799999999999</v>
+        <v>-4.4345</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.4859</v>
+        <v>-2.3081</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3876</v>
+        <v>-1.7841</v>
       </c>
       <c r="Q12" t="n">
-        <v>-12.6861</v>
+        <v>-8.3254</v>
       </c>
       <c r="R12" t="n">
-        <v>14.0736</v>
+        <v>6.5412</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6405</v>
+        <v>-0.2835</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5516999999999999</v>
+        <v>-0.6106</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1924</v>
+        <v>0.3270000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.7763</v>
+        <v>-2.0069</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0663</v>
+        <v>-0.337</v>
       </c>
       <c r="X12" t="n">
-        <v>-5.842600000000001</v>
+        <v>-1.6699</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BAMADU</t>
+          <t>K. DOMINGOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-12.1404</v>
+        <v>-15.2041</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7022</v>
+        <v>-4.888599999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.4381</v>
+        <v>-10.3156</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.055099999999999</v>
+        <v>2.385800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2692000000000001</v>
+        <v>6.503399999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>-8.324300000000001</v>
+        <v>-4.1171</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0777</v>
+        <v>15.689</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1936</v>
+        <v>13.6801</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2712</v>
+        <v>2.009</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.9775</v>
+        <v>-13.3032</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9244</v>
+        <v>-7.1768</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.0531</v>
+        <v>-6.1264</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3877</v>
+        <v>-17.0471</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.153700000000001</v>
+        <v>-32.7067</v>
       </c>
       <c r="R13" t="n">
-        <v>3.7662</v>
+        <v>15.6597</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4203</v>
+        <v>3.5823</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6075</v>
+        <v>4.2578</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1872</v>
+        <v>-0.6753</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2775</v>
+        <v>-4.1252</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1367</v>
+        <v>7.8714</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4142</v>
+        <v>-11.9966</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. JIMENEZ MARTINEZ</t>
+          <t>L. MAERIEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>-14.3233</v>
+        <v>-16.2503</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.4702</v>
+        <v>-8.1069</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.8528</v>
+        <v>-8.1434</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.8337</v>
+        <v>-5.403</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.3382</v>
+        <v>-0.4150999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.4955</v>
+        <v>-4.988099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.0913</v>
+        <v>1.1405</v>
       </c>
       <c r="K14" t="n">
-        <v>0.09630000000000005</v>
+        <v>3.4643</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.1875</v>
+        <v>-2.3237</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.7424</v>
+        <v>-6.5435</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.4345</v>
+        <v>-3.8794</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.3081</v>
+        <v>-2.6643</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.7841</v>
+        <v>-1.1894</v>
       </c>
       <c r="Q14" t="n">
-        <v>-8.3254</v>
+        <v>-9.1182</v>
       </c>
       <c r="R14" t="n">
-        <v>6.5412</v>
+        <v>7.9289</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3014999999999999</v>
+        <v>-1.6356</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2833999999999998</v>
+        <v>0.01159999999999983</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01809999999999995</v>
+        <v>-1.6474</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.0069</v>
+        <v>-8.0223</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.337</v>
+        <v>-0.1408</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6699</v>
+        <v>-7.881399999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MAERIEN</t>
+          <t>S. OKUNGHAE FRANCIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>-16.4981</v>
+        <v>-16.3221</v>
       </c>
       <c r="E15" t="n">
-        <v>-7.6664</v>
+        <v>-6.348699999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-8.8316</v>
+        <v>-9.9735</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.403</v>
+        <v>-7.8755</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.4150999999999999</v>
+        <v>-3.8132</v>
       </c>
       <c r="I15" t="n">
-        <v>-4.988099999999999</v>
+        <v>-4.0623</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1405</v>
+        <v>-0.3974</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4643</v>
+        <v>1.2383</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.3237</v>
+        <v>-1.6355</v>
       </c>
       <c r="M15" t="n">
-        <v>-6.5435</v>
+        <v>-7.4784</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.8794</v>
+        <v>-5.051699999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.6643</v>
+        <v>-2.4267</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1894</v>
+        <v>-0.1982000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-9.1182</v>
+        <v>-6.3431</v>
       </c>
       <c r="R15" t="n">
-        <v>7.9289</v>
+        <v>6.1448</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8834</v>
+        <v>-3.2238</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4521999999999999</v>
+        <v>-1.4191</v>
       </c>
       <c r="U15" t="n">
-        <v>-2.3355</v>
+        <v>-1.8048</v>
       </c>
       <c r="V15" t="n">
-        <v>-8.0223</v>
+        <v>-5.0246</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1408</v>
+        <v>1.8107</v>
       </c>
       <c r="X15" t="n">
-        <v>-7.881399999999999</v>
+        <v>-6.8352</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. OKUNGHAE FRANCIS</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,70 +1654,70 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-18.83</v>
+        <v>-17.7497</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.7191</v>
+        <v>-0.8901999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.1109</v>
+        <v>-16.8594</v>
       </c>
       <c r="G16" t="n">
-        <v>-7.8755</v>
+        <v>-19.7762</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.8132</v>
+        <v>1.625</v>
       </c>
       <c r="I16" t="n">
-        <v>-4.0623</v>
+        <v>-21.4008</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3974</v>
+        <v>24.5237</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2383</v>
+        <v>24.2178</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.6355</v>
+        <v>0.3059000000000002</v>
       </c>
       <c r="M16" t="n">
-        <v>-7.4784</v>
+        <v>-44.2998</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.051699999999999</v>
+        <v>-22.5929</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4267</v>
+        <v>-21.707</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1982000000000001</v>
+        <v>-11.1002</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.3431</v>
+        <v>-63.2329</v>
       </c>
       <c r="R16" t="n">
-        <v>6.1448</v>
+        <v>52.1325</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.7318</v>
+        <v>8.0299</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.7894</v>
+        <v>2.9994</v>
       </c>
       <c r="U16" t="n">
-        <v>-2.9424</v>
+        <v>5.0305</v>
       </c>
       <c r="V16" t="n">
-        <v>-5.0246</v>
+        <v>5.097099999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8107</v>
+        <v>34.8202</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.8352</v>
+        <v>-29.7231</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>23</v>
       </c>
       <c r="D17" t="n">
-        <v>-21.1418</v>
+        <v>-19.5599</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.1449</v>
+        <v>-11.3174</v>
       </c>
       <c r="F17" t="n">
-        <v>-8.9968</v>
+        <v>-8.242600000000001</v>
       </c>
       <c r="G17" t="n">
         <v>-18.5074</v>
@@ -1780,13 +1780,13 @@
         <v>22.3991</v>
       </c>
       <c r="S17" t="n">
-        <v>-4.6796</v>
+        <v>-3.097599999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-3.2064</v>
+        <v>-2.3788</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.473</v>
+        <v>-0.7185999999999997</v>
       </c>
       <c r="V17" t="n">
         <v>-3.1083</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. SENZI KITAMBO</t>
+          <t>R. URBANO MORENO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>-21.6228</v>
+        <v>-25.3024</v>
       </c>
       <c r="E18" t="n">
-        <v>-20.7793</v>
+        <v>-16.5026</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8434000000000001</v>
+        <v>-8.7997</v>
       </c>
       <c r="G18" t="n">
-        <v>-19.5037</v>
+        <v>-16.5961</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.295100000000001</v>
+        <v>-4.263299999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-14.2085</v>
+        <v>-12.3328</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4224000000000006</v>
+        <v>-3.582</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1248</v>
+        <v>3.1782</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.547</v>
+        <v>-6.7602</v>
       </c>
       <c r="M18" t="n">
-        <v>-19.0816</v>
+        <v>-13.0139</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.4202</v>
+        <v>-7.4412</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.6614</v>
+        <v>-5.5726</v>
       </c>
       <c r="P18" t="n">
-        <v>-6.5413</v>
+        <v>-4.5594</v>
       </c>
       <c r="Q18" t="n">
-        <v>-27.5529</v>
+        <v>-14.4701</v>
       </c>
       <c r="R18" t="n">
-        <v>21.0116</v>
+        <v>9.911099999999999</v>
       </c>
       <c r="S18" t="n">
-        <v>5.5852</v>
+        <v>-2.2329</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4460000000000002</v>
+        <v>-2.4639</v>
       </c>
       <c r="U18" t="n">
-        <v>5.139</v>
+        <v>0.2310999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.1629</v>
+        <v>-1.9141</v>
       </c>
       <c r="W18" t="n">
-        <v>6.7499</v>
+        <v>4.0137</v>
       </c>
       <c r="X18" t="n">
-        <v>-7.912599999999999</v>
+        <v>-5.9279</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. URBANO MORENO</t>
+          <t>E. SENZI KITAMBO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>-25.8868</v>
+        <v>-26.7625</v>
       </c>
       <c r="E19" t="n">
-        <v>-16.9559</v>
+        <v>-22.5837</v>
       </c>
       <c r="F19" t="n">
-        <v>-8.931000000000001</v>
+        <v>-4.1789</v>
       </c>
       <c r="G19" t="n">
-        <v>-16.5961</v>
+        <v>-19.5037</v>
       </c>
       <c r="H19" t="n">
-        <v>-4.263299999999999</v>
+        <v>-5.295100000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-12.3328</v>
+        <v>-14.2085</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.582</v>
+        <v>-0.4224000000000006</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1782</v>
+        <v>5.1248</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.7602</v>
+        <v>-5.547</v>
       </c>
       <c r="M19" t="n">
-        <v>-13.0139</v>
+        <v>-19.0816</v>
       </c>
       <c r="N19" t="n">
-        <v>-7.4412</v>
+        <v>-10.4202</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.5726</v>
+        <v>-8.6614</v>
       </c>
       <c r="P19" t="n">
-        <v>-4.5594</v>
+        <v>-6.5413</v>
       </c>
       <c r="Q19" t="n">
-        <v>-14.4701</v>
+        <v>-27.5529</v>
       </c>
       <c r="R19" t="n">
-        <v>9.911099999999999</v>
+        <v>21.0116</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.8173</v>
+        <v>0.4454000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-2.9173</v>
+        <v>-1.3581</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09989999999999988</v>
+        <v>1.8037</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.9141</v>
+        <v>-1.1629</v>
       </c>
       <c r="W19" t="n">
-        <v>4.0137</v>
+        <v>6.7499</v>
       </c>
       <c r="X19" t="n">
-        <v>-5.9279</v>
+        <v>-7.912599999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>-46.8762</v>
+        <v>-41.2778</v>
       </c>
       <c r="E20" t="n">
-        <v>-36.5421</v>
+        <v>-34.1698</v>
       </c>
       <c r="F20" t="n">
-        <v>-10.3337</v>
+        <v>-7.1081</v>
       </c>
       <c r="G20" t="n">
         <v>-22.6064</v>
@@ -2014,13 +2014,13 @@
         <v>21.8045</v>
       </c>
       <c r="S20" t="n">
-        <v>-9.371</v>
+        <v>-3.7728</v>
       </c>
       <c r="T20" t="n">
-        <v>-4.3734</v>
+        <v>-2.0013</v>
       </c>
       <c r="U20" t="n">
-        <v>-4.9976</v>
+        <v>-1.7716</v>
       </c>
       <c r="V20" t="n">
         <v>-5.9782</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. REYES ORTEGA</t>
+          <t>F. DAYER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,76 +2044,76 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D21" t="n">
-        <v>-53.7692</v>
+        <v>-41.9496</v>
       </c>
       <c r="E21" t="n">
-        <v>-44.5469</v>
+        <v>-37.0959</v>
       </c>
       <c r="F21" t="n">
-        <v>-9.222100000000001</v>
+        <v>-4.853400000000001</v>
       </c>
       <c r="G21" t="n">
-        <v>-26.2529</v>
+        <v>8.989500000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-9.1197</v>
+        <v>0.5651999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-17.1331</v>
+        <v>8.424599999999998</v>
       </c>
       <c r="J21" t="n">
-        <v>-12.7222</v>
+        <v>51.2954</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.105200000000001</v>
+        <v>24.5085</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.617</v>
+        <v>26.787</v>
       </c>
       <c r="M21" t="n">
-        <v>-13.5306</v>
+        <v>-42.306</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.0145</v>
+        <v>-23.9433</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.516400000000001</v>
+        <v>-18.3625</v>
       </c>
       <c r="P21" t="n">
-        <v>-14.0738</v>
+        <v>-77.70350000000001</v>
       </c>
       <c r="Q21" t="n">
-        <v>-31.5174</v>
+        <v>-126.8626</v>
       </c>
       <c r="R21" t="n">
-        <v>17.4435</v>
+        <v>49.1595</v>
       </c>
       <c r="S21" t="n">
-        <v>-5.249499999999999</v>
+        <v>-6.8324</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.8324</v>
+        <v>-8.968500000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-2.4168</v>
+        <v>2.1358</v>
       </c>
       <c r="V21" t="n">
-        <v>-8.193200000000001</v>
+        <v>33.5969</v>
       </c>
       <c r="W21" t="n">
-        <v>2.525</v>
+        <v>47.4395</v>
       </c>
       <c r="X21" t="n">
-        <v>-10.7182</v>
+        <v>-13.8427</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. DAYER</t>
+          <t>J. REYES ORTEGA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,70 +2122,70 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D22" t="n">
-        <v>-60.143</v>
+        <v>-49.0026</v>
       </c>
       <c r="E22" t="n">
-        <v>-52.1756</v>
+        <v>-41.7276</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.967499999999999</v>
+        <v>-7.274999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>8.989500000000001</v>
+        <v>-26.2529</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5651999999999999</v>
+        <v>-9.1197</v>
       </c>
       <c r="I22" t="n">
-        <v>8.424599999999998</v>
+        <v>-17.1331</v>
       </c>
       <c r="J22" t="n">
-        <v>51.2954</v>
+        <v>-12.7222</v>
       </c>
       <c r="K22" t="n">
-        <v>24.5085</v>
+        <v>-5.105200000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>26.787</v>
+        <v>-7.617</v>
       </c>
       <c r="M22" t="n">
-        <v>-42.306</v>
+        <v>-13.5306</v>
       </c>
       <c r="N22" t="n">
-        <v>-23.9433</v>
+        <v>-4.0145</v>
       </c>
       <c r="O22" t="n">
-        <v>-18.3625</v>
+        <v>-9.516400000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-77.70350000000001</v>
+        <v>-14.0738</v>
       </c>
       <c r="Q22" t="n">
-        <v>-126.8626</v>
+        <v>-31.5174</v>
       </c>
       <c r="R22" t="n">
-        <v>49.1595</v>
+        <v>17.4435</v>
       </c>
       <c r="S22" t="n">
-        <v>-25.026</v>
+        <v>-0.4829999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-24.0473</v>
+        <v>-0.01320000000000005</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9784999999999997</v>
+        <v>-0.4699</v>
       </c>
       <c r="V22" t="n">
-        <v>33.5969</v>
+        <v>-8.193200000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>47.4395</v>
+        <v>2.525</v>
       </c>
       <c r="X22" t="n">
-        <v>-13.8427</v>
+        <v>-10.7182</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>26</v>
       </c>
       <c r="D23" t="n">
-        <v>-70.0583</v>
+        <v>-55.949</v>
       </c>
       <c r="E23" t="n">
-        <v>-54.145</v>
+        <v>-42.4901</v>
       </c>
       <c r="F23" t="n">
-        <v>-15.9133</v>
+        <v>-13.459</v>
       </c>
       <c r="G23" t="n">
         <v>-22.0812</v>
@@ -2248,13 +2248,13 @@
         <v>53.9168</v>
       </c>
       <c r="S23" t="n">
-        <v>-22.4667</v>
+        <v>-8.3576</v>
       </c>
       <c r="T23" t="n">
-        <v>-19.8141</v>
+        <v>-8.1592</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.6521</v>
+        <v>-0.1983999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>9.7735</v>
@@ -2281,13 +2281,13 @@
         <v>26</v>
       </c>
       <c r="D24" t="n">
-        <v>-383.2765000000001</v>
+        <v>-359.544</v>
       </c>
       <c r="E24" t="n">
-        <v>-247.6153</v>
+        <v>-239.5038</v>
       </c>
       <c r="F24" t="n">
-        <v>-135.6595</v>
+        <v>-120.04</v>
       </c>
       <c r="G24" t="n">
         <v>-163.6438</v>
@@ -2326,13 +2326,13 @@
         <v>355.8096</v>
       </c>
       <c r="S24" t="n">
-        <v>-51.54349999999999</v>
+        <v>-27.8121</v>
       </c>
       <c r="T24" t="n">
-        <v>-37.2628</v>
+        <v>-29.1512</v>
       </c>
       <c r="U24" t="n">
-        <v>-14.2806</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
         <v>19.2335</v>
